--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,11 @@
           <t>application</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pcieSlots</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,6 +534,11 @@
           <t>hpc|storage</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x8|OCP3.0 x8</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -586,6 +596,11 @@
           <t>hpc|storage|hci</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x8|OCP3.0 x8</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -643,6 +658,11 @@
           <t>ai|ai-training|hpc</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -700,6 +720,11 @@
           <t>ai|ai-inference|visual-computing</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -757,6 +782,11 @@
           <t>ai|ai-training|hpc</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>PCIe x16 double width|PCIe x16|PCIe x16|PCIe x8|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -814,6 +844,11 @@
           <t>hpc</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x8|OCP3.0 x8</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -871,6 +906,11 @@
           <t>edge|storage</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x8|OCP3.0 x8</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -928,6 +968,11 @@
           <t>ai|ai-training|hpc</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -985,6 +1030,11 @@
           <t>ai|ai-training</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1042,6 +1092,11 @@
           <t>ai|ai-training</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>PCIe x16 double width|PCIe x16|PCIe x16|PCIe x8|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1099,6 +1154,11 @@
           <t>edge</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x8|OCP3.0 x8</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1156,6 +1216,11 @@
           <t>edge|ai-inference</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x8|OCP3.0 x8</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1213,6 +1278,11 @@
           <t>storage|hci</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x8|OCP3.0 x8</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1270,6 +1340,11 @@
           <t>hpc|storage</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x8|OCP3.0 x8</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1327,6 +1402,11 @@
           <t>ai|ai-training|hpc</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1384,6 +1464,11 @@
           <t>ai|ai-inference</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1441,6 +1526,11 @@
           <t>ai|ai-training</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1498,6 +1588,11 @@
           <t>ai|ai-training|hpc</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1555,6 +1650,11 @@
           <t>ai|hpc</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1612,6 +1712,11 @@
           <t>ai|ai-training|hpc</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PCIe x16 double width|PCIe x16|PCIe x16|PCIe x8|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1669,6 +1774,11 @@
           <t>ai|ai-training</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PCIe x16 double width|PCIe x16|PCIe x16|PCIe x8|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1726,6 +1836,11 @@
           <t>ai|ai-training</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PCIe x16 double width|PCIe x16 double width|PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1783,6 +1898,11 @@
           <t>ai|ai-training</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1840,6 +1960,11 @@
           <t>visual-computing|ai-inference</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>PCIe x16 double width|PCIe x16|PCIe x16|PCIe x8|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1897,6 +2022,11 @@
           <t>ai|ai-inference|hpc</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1954,6 +2084,11 @@
           <t>ai|ai-training</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2011,6 +2146,11 @@
           <t>ai|ai-training|hpc</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>PCIe x16 double width|PCIe x16 double width|PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2068,6 +2208,11 @@
           <t>ai|ai-training|hpc</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>PCIe x16 double width|PCIe x16 double width|PCIe x16|PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2125,6 +2270,11 @@
           <t>edge|hci</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x8|OCP3.0 x8</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2182,6 +2332,11 @@
           <t>hpc|storage</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2239,6 +2394,11 @@
           <t>edge|hci</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x8|OCP3.0 x8</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2296,6 +2456,11 @@
           <t>hpc|storage|hci</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2353,6 +2518,11 @@
           <t>ai|ai-training|hpc</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>PCIe x16 double width|PCIe x16|PCIe x16|PCIe x8|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2410,6 +2580,11 @@
           <t>ai|ai-training</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>PCIe x16 double width|PCIe x16 double width|PCIe x16|PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2465,6 +2640,11 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>ai|ai-training|ai-inference</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>PCIe x16|PCIe x16|PCIe x8|PCIe x8|OCP3.0 x16</t>
         </is>
       </c>
     </row>
